--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484206_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484206_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6405</v>
+        <v>8.0814</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3397</v>
+        <v>5.2163</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3009</v>
+        <v>2.8651</v>
       </c>
       <c r="G2" t="n">
         <v>5.2405</v>
@@ -610,13 +610,13 @@
         <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5601</v>
+        <v>2.0009</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8109</v>
+        <v>1.6874</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7492</v>
+        <v>0.3135</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3324</v>
+        <v>2.4482</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2956</v>
+        <v>1.9893</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0368</v>
+        <v>0.4589</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.005</v>
+        <v>-0.2255</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3162</v>
+        <v>-2.4917</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6887</v>
+        <v>2.2663</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1153</v>
+        <v>2.1618</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2367</v>
+        <v>-0.9146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1214</v>
+        <v>3.0764</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8897</v>
+        <v>-2.3872</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0795</v>
+        <v>-1.5771</v>
       </c>
       <c r="O3" t="n">
         <v>-0.8101</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5162</v>
+        <v>2.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>6.6341</v>
+        <v>0.7202</v>
       </c>
       <c r="T3" t="n">
-        <v>6.2238</v>
+        <v>0.8042</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4103</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0192</v>
+        <v>2.2255</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2258</v>
+        <v>1.1119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7934</v>
+        <v>1.1136</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.27</v>
+        <v>0.6586</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4567</v>
+        <v>0.9691</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7266</v>
+        <v>-0.3105</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1685</v>
+        <v>1.8229</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3548</v>
+        <v>1.1883</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1863</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4384</v>
+        <v>-1.1643</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8982</v>
+        <v>-0.2192</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5403</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5897</v>
+        <v>0.9809</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7567</v>
+        <v>1.4377</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8329</v>
+        <v>-0.4568</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3464</v>
+        <v>2.202</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5052</v>
+        <v>-0.3445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8413</v>
+        <v>2.5466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6586</v>
+        <v>-1.005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9691</v>
+        <v>-0.3162</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3105</v>
+        <v>-0.6887</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8229</v>
+        <v>-0.1153</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1883</v>
+        <v>-0.2367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1643</v>
+        <v>-0.8897</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2192</v>
+        <v>-0.0795</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.8101</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7348</v>
+        <v>3.5162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1018</v>
+        <v>2.5038</v>
       </c>
       <c r="T5" t="n">
-        <v>0.831</v>
+        <v>2.5837</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7292</v>
+        <v>-0.0799</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1826</v>
+        <v>1.6221</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0456</v>
+        <v>1.349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1369</v>
+        <v>0.2731</v>
       </c>
       <c r="G6" t="n">
         <v>0.06850000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4952</v>
+        <v>-0.0557</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1816</v>
+        <v>0.1218</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3137</v>
+        <v>-0.1775</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7143</v>
+        <v>1.5562</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.517</v>
+        <v>1.2258</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2314</v>
+        <v>0.3304</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5528</v>
+        <v>-0.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1481</v>
+        <v>1.4567</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4047</v>
+        <v>-1.7266</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6127</v>
+        <v>1.1685</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>2.3548</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>-1.1863</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0599</v>
+        <v>-1.4384</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2095</v>
+        <v>-0.8982</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2694</v>
+        <v>-0.5403</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3775</v>
+        <v>1.1267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1816</v>
+        <v>0.7567</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.196</v>
+        <v>0.3699</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
         <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5774</v>
+        <v>0.7259</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4726</v>
+        <v>-0.3148</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1048</v>
+        <v>1.0407</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2255</v>
+        <v>-0.5528</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4917</v>
+        <v>-0.1481</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2663</v>
+        <v>-0.4047</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1618</v>
+        <v>-0.6127</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9146</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0764</v>
+        <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3872</v>
+        <v>0.0599</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5771</v>
+        <v>-0.2095</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8101</v>
+        <v>0.2694</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9301</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1506</v>
+        <v>-0.366</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7125</v>
+        <v>0.0207</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4381</v>
+        <v>-0.3866</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6565</v>
+        <v>0.2021</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4581</v>
+        <v>0.3068</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1984</v>
+        <v>-0.1047</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6119</v>
+        <v>-2.2966</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8427</v>
+        <v>-3.0661</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7692</v>
+        <v>0.7694</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5927</v>
+        <v>-1.3377</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6332</v>
+        <v>-2.5122</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>1.1745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0192</v>
+        <v>-0.9589</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2095</v>
+        <v>-0.5538</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8097</v>
+        <v>-0.4051</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7087</v>
+        <v>0.6858</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1073</v>
+        <v>0.4259</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6015</v>
+        <v>0.2599</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2735</v>
+        <v>0.0549</v>
       </c>
       <c r="W9" t="n">
         <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0549</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8441</v>
+        <v>0.0591</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.1486</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2408</v>
+        <v>-0.0895</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2966</v>
+        <v>-1.6119</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0661</v>
+        <v>-0.8427</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7694</v>
+        <v>-0.7692</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3377</v>
+        <v>-0.5927</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5122</v>
+        <v>-0.6332</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1745</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9589</v>
+        <v>-1.0192</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5538</v>
+        <v>-0.2095</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4051</v>
+        <v>-0.8097</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3604</v>
+        <v>0.0069</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4842</v>
+        <v>0.4994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1238</v>
+        <v>-0.4925</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0549</v>
+        <v>1.2735</v>
       </c>
       <c r="W10" t="n">
         <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1638</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6756</v>
+        <v>-0.4387</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2181</v>
+        <v>-2.3081</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5426</v>
+        <v>1.8694</v>
       </c>
       <c r="G11" t="n">
         <v>0.6695</v>
@@ -1312,13 +1312,13 @@
         <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1963</v>
+        <v>0.0406</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3356</v>
+        <v>0.5744</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8607</v>
+        <v>-0.5339</v>
       </c>
       <c r="V11" t="n">
         <v>0.6093</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.991</v>
+        <v>-4.0381</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3815</v>
+        <v>-5.6737</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3905</v>
+        <v>1.6356</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3009</v>
@@ -1390,13 +1390,13 @@
         <v>3.7115</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5766</v>
+        <v>0.3763</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0989</v>
+        <v>0.6089</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4777</v>
+        <v>-0.2326</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
@@ -1423,37 +1423,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.6456</v>
+        <v>14.6457</v>
       </c>
       <c r="E13" t="n">
-        <v>2.706500000000001</v>
+        <v>2.7066</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9394</v>
+        <v>11.9392</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6256</v>
+        <v>-3.625600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2519999999999989</v>
+        <v>-0.2519999999999996</v>
       </c>
       <c r="I13" t="n">
         <v>-3.3734</v>
       </c>
       <c r="J13" t="n">
-        <v>6.665800000000001</v>
+        <v>6.665799999999999</v>
       </c>
       <c r="K13" t="n">
         <v>4.6365</v>
       </c>
       <c r="L13" t="n">
-        <v>2.029300000000001</v>
+        <v>2.0293</v>
       </c>
       <c r="M13" t="n">
         <v>-10.2913</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.8885</v>
+        <v>-4.888500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-5.4028</v>
@@ -1468,13 +1468,13 @@
         <v>25.3945</v>
       </c>
       <c r="S13" t="n">
-        <v>8.020400000000002</v>
+        <v>8.0204</v>
       </c>
       <c r="T13" t="n">
-        <v>9.520700000000001</v>
+        <v>9.520800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5007</v>
+        <v>-1.5005</v>
       </c>
       <c r="V13" t="n">
         <v>2.4372</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.386</v>
+        <v>4.3262</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5974</v>
+        <v>5.4985</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7886</v>
+        <v>-1.1723</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7684</v>
+        <v>3.4774</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2868</v>
+        <v>1.0893</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4816</v>
+        <v>2.3881</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7747</v>
+        <v>6.4187</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6971000000000001</v>
+        <v>2.681</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0776</v>
+        <v>3.7377</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9938</v>
+        <v>-2.9413</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5897</v>
+        <v>-1.5917</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4041</v>
+        <v>-1.3496</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6724</v>
+        <v>-0.714</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6124</v>
+        <v>0.2519</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9659</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.015</v>
+        <v>3.7534</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2963</v>
+        <v>2.5863</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2813</v>
+        <v>1.1672</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4774</v>
+        <v>3.7684</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0893</v>
+        <v>1.2868</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3881</v>
+        <v>2.4816</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4187</v>
+        <v>2.7747</v>
       </c>
       <c r="K15" t="n">
-        <v>2.681</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7377</v>
+        <v>2.0776</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9413</v>
+        <v>0.9938</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5917</v>
+        <v>0.5897</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3496</v>
+        <v>0.4041</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0251</v>
+        <v>0.0399</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0497</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0748</v>
+        <v>-0.5614</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3063</v>
+        <v>2.3788</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2661</v>
+        <v>0.3672</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0402</v>
+        <v>2.0116</v>
       </c>
       <c r="G16" t="n">
         <v>2.8886</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5823</v>
+        <v>-0.5097</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1678</v>
+        <v>-0.0667</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4145</v>
+        <v>-0.4431</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0424</v>
+        <v>1.3794</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3819</v>
+        <v>1.5841</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3395</v>
+        <v>-0.2047</v>
       </c>
       <c r="G17" t="n">
         <v>3.0509</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2039</v>
+        <v>-1.8668</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4171</v>
+        <v>-1.2823</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0712</v>
+        <v>-0.7965</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0742</v>
+        <v>-2.7708</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0029</v>
+        <v>1.9744</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2917</v>
@@ -1858,13 +1858,13 @@
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2288</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2751</v>
+        <v>0.0283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9538</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8381</v>
+        <v>-1.9405</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1567</v>
+        <v>-1.2579</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6813</v>
+        <v>-0.6827</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2061</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2999</v>
+        <v>-0.4024</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>-0.1395</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2615</v>
+        <v>-0.2629</v>
       </c>
       <c r="V19" t="n">
         <v>0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0781</v>
+        <v>-1.9991</v>
       </c>
       <c r="E20" t="n">
         <v>-3.5875</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5094</v>
+        <v>1.5884</v>
       </c>
       <c r="G20" t="n">
         <v>2.0195</v>
@@ -2014,13 +2014,13 @@
         <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9954</v>
+        <v>-1.9164</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2805</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7149</v>
+        <v>-1.6359</v>
       </c>
       <c r="V20" t="n">
         <v>1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1929</v>
+        <v>-3.7742</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0982</v>
+        <v>-2.8959</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0948</v>
+        <v>-0.8782</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3448</v>
@@ -2092,13 +2092,13 @@
         <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3087</v>
+        <v>0.1101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5476</v>
+        <v>0.7499</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8563</v>
+        <v>-0.6398</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.158</v>
+        <v>-5.3524</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5595</v>
+        <v>-2.8629</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5984</v>
+        <v>-2.4895</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9966</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3698</v>
+        <v>0.1754</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7016</v>
+        <v>0.3983</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3318</v>
+        <v>-0.2229</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7731</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9464</v>
+        <v>-5.3642</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1221</v>
+        <v>-3.9199</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8243</v>
+        <v>-1.4443</v>
       </c>
       <c r="G23" t="n">
         <v>-4.536</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8792</v>
+        <v>-0.2971</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1707</v>
+        <v>0.3729</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.05</v>
+        <v>-0.67</v>
       </c>
       <c r="V23" t="n">
         <v>0.0549</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1107</v>
+        <v>-5.9085</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8827</v>
+        <v>-4.6805</v>
       </c>
       <c r="F24" t="n">
         <v>-1.228</v>
@@ -2326,10 +2326,10 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5393</v>
+        <v>-0.337</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.033</v>
+        <v>0.1693</v>
       </c>
       <c r="U24" t="n">
         <v>-0.5063</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.6457</v>
+        <v>-13.2976</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.9392</v>
+        <v>-11.9393</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7065</v>
+        <v>-1.3581</v>
       </c>
       <c r="G25" t="n">
         <v>3.625600000000001</v>
@@ -2404,13 +2404,13 @@
         <v>17.5808</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.0204</v>
+        <v>-6.6721</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5004</v>
+        <v>1.5006</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.521000000000001</v>
+        <v>-8.1729</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4373</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484206_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484206_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ CHAVARRIA</t>
+          <t>B. RODRIGUEZ CHAVARRIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1111,67 +1151,72 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2021</v>
+        <v>0.607</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3068</v>
+        <v>0.607</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1047</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2966</v>
+        <v>0.607</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0661</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7694</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3377</v>
+        <v>0.607</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5122</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1745</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9589</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5538</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6858</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4259</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2599</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4387</v>
+        <v>-0.4049</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3081</v>
+        <v>-0.3002</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8694</v>
+        <v>-0.1047</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6695</v>
+        <v>-2.9036</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9105</v>
+        <v>-3.0661</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.241</v>
+        <v>0.1625</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6103</v>
+        <v>-1.9447</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3111</v>
+        <v>-2.5122</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7007</v>
+        <v>0.5675</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0591</v>
+        <v>-0.9589</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5994</v>
+        <v>-0.5538</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5403</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0406</v>
+        <v>0.6858</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5744</v>
+        <v>0.4259</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5339</v>
+        <v>0.2599</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6093</v>
+        <v>0.0549</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0381</v>
+        <v>-0.4387</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6737</v>
+        <v>-2.3081</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6356</v>
+        <v>1.8694</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3009</v>
+        <v>0.6695</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4687</v>
+        <v>1.9105</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8322</v>
+        <v>-1.241</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4576</v>
+        <v>0.6103</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5705</v>
+        <v>1.3111</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8871</v>
+        <v>-0.7007</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8433</v>
+        <v>0.0591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8982</v>
+        <v>0.5994</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.5403</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q12" t="n">
         <v>-4.1022</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7115</v>
+        <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3763</v>
+        <v>0.0406</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6089</v>
+        <v>0.5744</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2326</v>
+        <v>-0.5339</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.6457</v>
+        <v>-4.0381</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7066</v>
+        <v>-5.6737</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9392</v>
+        <v>1.6356</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.625600000000001</v>
+        <v>-4.3009</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2519999999999996</v>
+        <v>-1.4687</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3734</v>
+        <v>-2.8322</v>
       </c>
       <c r="J13" t="n">
-        <v>6.665799999999999</v>
+        <v>-2.4576</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6365</v>
+        <v>-0.5705</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0293</v>
+        <v>-1.8871</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.2913</v>
+        <v>-1.8433</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.888500000000001</v>
+        <v>-0.8982</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.4028</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8137</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5809</v>
+        <v>-4.1022</v>
       </c>
       <c r="R13" t="n">
-        <v>25.3945</v>
+        <v>3.7115</v>
       </c>
       <c r="S13" t="n">
-        <v>8.0204</v>
+        <v>0.3763</v>
       </c>
       <c r="T13" t="n">
-        <v>9.520800000000001</v>
+        <v>0.6089</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5005</v>
+        <v>-0.2326</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4372</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1004</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6634</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3262</v>
+        <v>14.6457</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4985</v>
+        <v>2.7066</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1723</v>
+        <v>11.9392</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4774</v>
+        <v>-3.6256</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0893</v>
+        <v>-0.2519999999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3881</v>
+        <v>-3.3733</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4187</v>
+        <v>6.665799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.681</v>
+        <v>4.636499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7377</v>
+        <v>2.0293</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9413</v>
+        <v>-10.2913</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5917</v>
+        <v>-4.8885</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3496</v>
+        <v>-5.4028</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>7.8137</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-17.5809</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>25.3945</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.714</v>
+        <v>8.0204</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2519</v>
+        <v>9.520800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9659</v>
+        <v>-1.5005</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.4372</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.1004</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.6634</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7534</v>
+        <v>4.3262</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5863</v>
+        <v>5.4985</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1672</v>
+        <v>-1.1723</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7684</v>
+        <v>3.4774</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2868</v>
+        <v>1.0893</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4816</v>
+        <v>2.3881</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7747</v>
+        <v>6.4187</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6971000000000001</v>
+        <v>2.681</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0776</v>
+        <v>3.7377</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9938</v>
+        <v>-2.9413</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5897</v>
+        <v>-1.5917</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4041</v>
+        <v>-1.3496</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0399</v>
+        <v>-0.714</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.2519</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5614</v>
+        <v>-0.9659</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3788</v>
+        <v>3.7534</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3672</v>
+        <v>2.5863</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0116</v>
+        <v>1.1672</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8886</v>
+        <v>3.7684</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4047</v>
+        <v>1.2868</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4838</v>
+        <v>2.4816</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4106</v>
+        <v>2.7747</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3492</v>
+        <v>2.0776</v>
       </c>
       <c r="M16" t="n">
-        <v>1.478</v>
+        <v>0.9938</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3433</v>
+        <v>0.5897</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1346</v>
+        <v>0.4041</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5097</v>
+        <v>0.0399</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0667</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4431</v>
+        <v>-0.5614</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3794</v>
+        <v>2.3788</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5841</v>
+        <v>0.3672</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2047</v>
+        <v>2.0116</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0509</v>
+        <v>2.8886</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3671</v>
+        <v>1.4047</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6838</v>
+        <v>1.4838</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1454</v>
+        <v>1.4106</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2701</v>
+        <v>0.0614</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8752</v>
+        <v>1.3492</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0945</v>
+        <v>1.478</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.903</v>
+        <v>1.3433</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8085</v>
+        <v>0.1346</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8668</v>
+        <v>-0.5097</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5846</v>
+        <v>-0.0667</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2823</v>
+        <v>-0.4431</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7965</v>
+        <v>1.3794</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7708</v>
+        <v>1.5841</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9744</v>
+        <v>-0.2047</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2917</v>
+        <v>3.0509</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1264</v>
+        <v>0.3671</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4181</v>
+        <v>2.6838</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4903</v>
+        <v>3.1454</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2635</v>
+        <v>1.2701</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2268</v>
+        <v>1.8752</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1986</v>
+        <v>-0.0945</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3899</v>
+        <v>-0.903</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8087</v>
+        <v>0.8085</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-1.8668</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0283</v>
+        <v>-0.5846</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.2823</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9405</v>
+        <v>-0.7965</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2579</v>
+        <v>-2.7708</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6827</v>
+        <v>1.9744</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2061</v>
+        <v>-0.2917</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6682</v>
+        <v>0.1264</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5379</v>
+        <v>-0.4181</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2235</v>
+        <v>-1.4903</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3697</v>
+        <v>-0.2635</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-1.2268</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9826</v>
+        <v>1.1986</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0379</v>
+        <v>0.3899</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9447</v>
+        <v>0.8087</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4024</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1395</v>
+        <v>0.0283</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2629</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9991</v>
+        <v>-1.9405</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5875</v>
+        <v>-1.2579</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5884</v>
+        <v>-0.6827</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0195</v>
+        <v>-2.2061</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8726</v>
+        <v>-0.6682</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1469</v>
+        <v>-1.5379</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1941</v>
+        <v>-0.2235</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0463</v>
+        <v>0.3697</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1478</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1746</v>
+        <v>-1.9826</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1737</v>
+        <v>-1.0379</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.001</v>
+        <v>-0.9447</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.3208</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.0556</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9164</v>
+        <v>-0.4024</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2805</v>
+        <v>-0.1395</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.6359</v>
+        <v>-0.2629</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7742</v>
+        <v>-1.9991</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8959</v>
+        <v>-3.5875</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8782</v>
+        <v>1.5884</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3448</v>
+        <v>2.0195</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8726</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1729</v>
+        <v>1.1469</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4331</v>
+        <v>2.1941</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3917</v>
+        <v>1.0463</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>1.1478</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7779</v>
+        <v>-0.1746</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5636</v>
+        <v>-0.1737</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2144</v>
+        <v>-0.001</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9301</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.0789</v>
+        <v>-6.0556</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1101</v>
+        <v>-1.9164</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7499</v>
+        <v>-0.2805</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6398</v>
+        <v>-1.6359</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BILBAO BORRAJO</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3524</v>
+        <v>-3.7742</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8629</v>
+        <v>-2.8959</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4895</v>
+        <v>-0.8782</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9966</v>
+        <v>-0.3448</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6324</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3642</v>
+        <v>-1.1729</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3077</v>
+        <v>1.4331</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3482</v>
+        <v>1.3917</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6889</v>
+        <v>-1.7779</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2842</v>
+        <v>-0.5636</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4047</v>
+        <v>-1.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-5.0789</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1754</v>
+        <v>0.1101</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3983</v>
+        <v>0.7499</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2229</v>
+        <v>-0.6398</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7731</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7731</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. BILBAO BORRAJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3642</v>
+        <v>-5.3524</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9199</v>
+        <v>-2.8629</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4443</v>
+        <v>-2.4895</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.536</v>
+        <v>-1.9966</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4296</v>
+        <v>-1.6324</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1064</v>
+        <v>-0.3642</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1441</v>
+        <v>-1.3077</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7128</v>
+        <v>-1.3482</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4313</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3919</v>
+        <v>-0.6889</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7168</v>
+        <v>-0.2842</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6751</v>
+        <v>-0.4047</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2971</v>
+        <v>0.1754</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3729</v>
+        <v>0.3983</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.67</v>
+        <v>-0.2229</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0549</v>
+        <v>-1.7731</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0549</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9085</v>
+        <v>-5.3642</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6805</v>
+        <v>-3.9199</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.228</v>
+        <v>-1.4443</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.204</v>
+        <v>-4.536</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0072</v>
+        <v>-3.4296</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2112</v>
+        <v>-1.1064</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9196</v>
+        <v>-2.1441</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6958</v>
+        <v>-1.7128</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.6155</v>
+        <v>-0.4313</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2844</v>
+        <v>-2.3919</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6887</v>
+        <v>-1.7168</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4043</v>
+        <v>-0.6751</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-2.1488</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.337</v>
+        <v>-0.2971</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1693</v>
+        <v>0.3729</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5063</v>
+        <v>-0.67</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-5.9085</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.6805</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.228</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.204</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.2112</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.9196</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.6155</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2844</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6887</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.337</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.5063</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484206_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-13.2976</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-11.9393</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-1.3581</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>3.625600000000001</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>0.2519999999999997</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>3.3735</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>10.2914</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>4.8886</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>5.4027</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-6.665699999999999</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-4.6367</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-2.0293</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>-7.813699999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-25.3945</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>17.5808</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-6.6721</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>1.5006</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>-8.1729</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-2.4373</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>1.6634</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-4.1005</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
